--- a/frontend/public/templates/sample_mcq_upload.xlsx
+++ b/frontend/public/templates/sample_mcq_upload.xlsx
@@ -26,9 +26,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -54,28 +55,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,15 +438,15 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="22.8" customWidth="1" min="2" max="2"/>
-    <col width="10.8" customWidth="1" min="3" max="3"/>
-    <col width="20.4" customWidth="1" min="4" max="4"/>
-    <col width="20.4" customWidth="1" min="5" max="5"/>
-    <col width="20.4" customWidth="1" min="6" max="6"/>
-    <col width="20.4" customWidth="1" min="7" max="7"/>
-    <col width="20.4" customWidth="1" min="8" max="8"/>
-    <col width="21.6" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -503,38 +497,48 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>What is 2+2?</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>What is the next number in the sequence: 2, 4, 8, 16, ?</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/templates/sample_mcq_upload.xlsx
+++ b/frontend/public/templates/sample_mcq_upload.xlsx
@@ -26,10 +26,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,8 +40,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F96331"/>
-        <bgColor rgb="00F96331"/>
+        <fgColor rgb="00f96331"/>
+        <bgColor rgb="00f96331"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,9 +436,9 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -497,48 +495,38 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>What is the next number in the sequence: 2, 4, 8, 16, ?</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/templates/sample_mcq_upload.xlsx
+++ b/frontend/public/templates/sample_mcq_upload.xlsx
@@ -54,19 +54,30 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,18 +444,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,22 +482,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Option 1 Text</t>
+          <t>Option 1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Option 2 Text</t>
+          <t>Option 2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Option 3 Text</t>
+          <t>Option 3</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Option 4 Text</t>
+          <t>Option 4</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -493,40 +505,490 @@
           <t>Correct Option</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Explanation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>What is the next number in the sequence: 2, 4, 8, 16, ?</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F2" t="n">
-        <v>32</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 1 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 1 and 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 2 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 2 and 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 3 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 3 and 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 4 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 4 and 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 5 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 5 and 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 6 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 6 and 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 7 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 7 and 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 8 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 8 and 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 9 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 9 and 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>What is the result of 10 multiplied by 5?</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Simple multiplication of 10 and 5.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/templates/sample_mcq_upload.xlsx
+++ b/frontend/public/templates/sample_mcq_upload.xlsx
@@ -444,19 +444,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,25 +491,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Option 1 Image</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Option 2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Option 2 Image</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Option 3 Image</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Option 4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Option 4 Image</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Correct Option</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -537,23 +561,43 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>data_chart_1.png</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_2.png</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_3.png</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_4.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 1 and 5.</t>
         </is>
@@ -585,23 +629,43 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>data_chart_1.png</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_2.png</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_3.png</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_4.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 2 and 5.</t>
         </is>
@@ -633,23 +697,43 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>data_chart_1.png</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_2.png</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_3.png</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_4.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 3 and 5.</t>
         </is>
@@ -681,23 +765,43 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>data_chart_1.png</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_2.png</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_3.png</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_4.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 4 and 5.</t>
         </is>
@@ -729,265 +833,45 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>data_chart_1.png</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_2.png</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_3.png</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>data_chart_4.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 5 and 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>APTITUDE</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>FRESHER</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>What is the result of 6 multiplied by 5?</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Simple multiplication of 6 and 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>APTITUDE</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>FRESHER</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>What is the result of 7 multiplied by 5?</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Simple multiplication of 7 and 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>APTITUDE</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>FRESHER</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>What is the result of 8 multiplied by 5?</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Simple multiplication of 8 and 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>APTITUDE</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>FRESHER</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>What is the result of 9 multiplied by 5?</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Simple multiplication of 9 and 5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>APTITUDE</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>FRESHER</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>What is the result of 10 multiplied by 5?</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Simple multiplication of 10 and 5.</t>
         </is>
       </c>
     </row>

--- a/frontend/public/templates/sample_mcq_upload.xlsx
+++ b/frontend/public/templates/sample_mcq_upload.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -491,45 +491,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Option 1 Image</t>
+          <t>Option 2</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 3</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Option 2 Image</t>
+          <t>Option 4</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Correct Option</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Option 3 Image</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Option 4 Image</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Correct Option</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
@@ -561,43 +541,23 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>data_chart_1.png</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>data_chart_2.png</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_3.png</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_4.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 1 and 5.</t>
         </is>
@@ -629,43 +589,23 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>data_chart_1.png</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>data_chart_2.png</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_3.png</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_4.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 2 and 5.</t>
         </is>
@@ -697,43 +637,23 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>data_chart_1.png</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>data_chart_2.png</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_3.png</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_4.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 3 and 5.</t>
         </is>
@@ -765,43 +685,23 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>data_chart_1.png</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>data_chart_2.png</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_3.png</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_4.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 4 and 5.</t>
         </is>
@@ -833,43 +733,23 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>data_chart_1.png</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>data_chart_2.png</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_3.png</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>data_chart_4.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Simple multiplication of 5 and 5.</t>
         </is>

--- a/frontend/public/templates/sample_mcq_upload.xlsx
+++ b/frontend/public/templates/sample_mcq_upload.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,8 +55,13 @@
         <bgColor rgb="00f96331"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF96331"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -67,16 +83,57 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,312 +501,322 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="35" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Question Id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Subject Code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Exam Level Code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Question Text</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Option 1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Option 4</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Correct Option</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="D2" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>What is the result of 1 multiplied by 5?</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>Simple multiplication of 1 and 5.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="D3" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>What is the result of 2 multiplied by 5?</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Simple multiplication of 2 and 5.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="D4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>What is the result of 3 multiplied by 5?</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>Simple multiplication of 3 and 5.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="D5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>What is the result of 4 multiplied by 5?</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Simple multiplication of 4 and 5.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="D6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>What is the result of 5 multiplied by 5?</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>Simple multiplication of 5 and 5.</t>
         </is>
